--- a/Apr_20_full_log/LHS_result.xlsx
+++ b/Apr_20_full_log/LHS_result.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PyCharm\Blueness\Apr_20_full_log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7F14377-4A7B-4D66-A4CB-A0FD5C9E300B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2795A73-4123-48A4-8629-51E779B03512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -366,719 +365,722 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECDB1A84-3938-46E6-A300-1AF68EBB2D04}">
   <dimension ref="A1:D97"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="16384" width="8.7265625" style="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1E-4</v>
-      </c>
-      <c r="B2">
+      <c r="A2" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.97027319000000001</v>
+      </c>
+      <c r="C2" s="1">
+        <v>6.1840059000000003E-2</v>
+      </c>
+      <c r="D2" s="1">
+        <v>13870.532992500001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.19203820799999999</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.35750437200000001</v>
+      </c>
+      <c r="D3" s="1">
+        <v>10792.6332475</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B4" s="1">
+        <v>0.152879814</v>
+      </c>
+      <c r="C4" s="1">
+        <v>4.745768E-3</v>
+      </c>
+      <c r="D4" s="1">
+        <v>9816.5989852500006</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>6.3274079999999996E-2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.51837422200000005</v>
+      </c>
+      <c r="D5" s="1">
+        <v>8286.1643399999994</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3.0869280000000001E-3</v>
+      </c>
+      <c r="C6" s="1">
+        <v>5.8427339999999996E-3</v>
+      </c>
+      <c r="D6" s="1">
+        <v>7589.2893402500004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B7" s="1">
+        <v>2.8054831999999998E-2</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2.5393009999999999E-3</v>
+      </c>
+      <c r="D7" s="1">
+        <v>7242.645939</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B8" s="1">
+        <v>2.3438180999999999E-2</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0.235570958</v>
+      </c>
+      <c r="D8" s="1">
+        <v>7167.6237312499998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B9" s="1">
+        <v>0.13645116500000001</v>
+      </c>
+      <c r="C9" s="1">
+        <v>4.0931093000000002E-2</v>
+      </c>
+      <c r="D9" s="1">
+        <v>6474.1021575000004</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B10" s="1">
+        <v>9.7710587000000002E-2</v>
+      </c>
+      <c r="C10" s="1">
+        <v>0.211593646</v>
+      </c>
+      <c r="D10" s="1">
+        <v>6402.72208125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1.2002880000000001E-3</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1.246567E-2</v>
+      </c>
+      <c r="D11" s="1">
+        <v>6312.9441622499999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B12" s="1">
+        <v>7.7832249000000006E-2</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1.0975659999999999E-3</v>
+      </c>
+      <c r="D12" s="1">
+        <v>5462.3096447500002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B13" s="1">
+        <v>4.4002681000000002E-2</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.9292954999999999E-2</v>
+      </c>
+      <c r="D13" s="1">
+        <v>5065.291878</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B14" s="1">
+        <v>0.36215188100000001</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0.148571812</v>
+      </c>
+      <c r="D14" s="1">
+        <v>4884.9175127500002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B15" s="1">
+        <v>0.23317315399999999</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.0254294999999999E-2</v>
+      </c>
+      <c r="D15" s="1">
+        <v>4505.40291875</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B16" s="1">
+        <v>3.3296083999999997E-2</v>
+      </c>
+      <c r="C16" s="1">
+        <v>8.4645748000000007E-2</v>
+      </c>
+      <c r="D16" s="1">
+        <v>4475.1998732499997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B17" s="1">
+        <v>0.653502209</v>
+      </c>
+      <c r="C17" s="1">
+        <v>9.7069930000000006E-3</v>
+      </c>
+      <c r="D17" s="1">
+        <v>3911.5133247499998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B18" s="1">
+        <v>6.4415100000000001E-3</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1.2496720000000001E-3</v>
+      </c>
+      <c r="D18" s="1">
+        <v>3890.2474617500002</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B19" s="1">
+        <v>4.9774750000000003E-3</v>
+      </c>
+      <c r="C19" s="1">
+        <v>5.4831019000000002E-2</v>
+      </c>
+      <c r="D19" s="1">
+        <v>3354.6065990000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B20" s="1">
+        <v>8.0714930000000008E-3</v>
+      </c>
+      <c r="C20" s="1">
+        <v>0.10003920500000001</v>
+      </c>
+      <c r="D20" s="1">
+        <v>3140.092005</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1.0292209E-2</v>
+      </c>
+      <c r="C21" s="1">
+        <v>8.4481729999999998E-3</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2598.3565992499998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1.2057157000000001E-2</v>
+      </c>
+      <c r="C22" s="1">
+        <v>0.81009397900000002</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2536.8813452499999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1.497338E-3</v>
+      </c>
+      <c r="C23" s="1">
+        <v>0.13228768099999999</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2434.4130709999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B24" s="1">
+        <v>0.29416244200000002</v>
+      </c>
+      <c r="C24" s="1">
+        <v>3.4769330000000002E-3</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2165.29505075</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B25" s="1">
+        <v>0.59090410599999998</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0.75721505499999997</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1912.052664925</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B26" s="1">
+        <v>0.51276795200000003</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1.6536929999999999E-3</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1821.16434</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B27" s="1">
+        <v>2.0133960000000002E-3</v>
+      </c>
+      <c r="C27" s="1">
+        <v>0.58600680999999999</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1453.20748725</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B28" s="1">
+        <v>2.674114E-3</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2.54425E-2</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1353.9435281999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B29" s="1">
+        <v>5.2151409000000003E-2</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1.6056401000000001E-2</v>
+      </c>
+      <c r="D29" s="1">
+        <v>899.07043136000004</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B30" s="1">
+        <v>1.3826926E-2</v>
+      </c>
+      <c r="C30" s="1">
+        <v>3.7099310000000001E-3</v>
+      </c>
+      <c r="D30" s="1">
+        <v>813.2296953</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B31" s="1">
+        <v>3.764926E-3</v>
+      </c>
+      <c r="C31" s="1">
+        <v>0.28711551000000002</v>
+      </c>
+      <c r="D31" s="1">
+        <v>566.81472080000003</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B32" s="1">
         <v>1.858829E-3</v>
       </c>
-      <c r="C2">
+      <c r="C32" s="1">
         <v>2.0690999999999999E-3</v>
       </c>
-      <c r="D2">
+      <c r="D32" s="1">
         <v>-27.382614207500001</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>1E-4</v>
-      </c>
-      <c r="B3">
-        <v>3.764926E-3</v>
-      </c>
-      <c r="C3">
-        <v>0.28711551000000002</v>
-      </c>
-      <c r="D3">
-        <v>566.81472080000003</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>1E-4</v>
-      </c>
-      <c r="B4">
-        <v>0.51276795200000003</v>
-      </c>
-      <c r="C4">
-        <v>1.6536929999999999E-3</v>
-      </c>
-      <c r="D4">
-        <v>1821.16434</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>1E-4</v>
-      </c>
-      <c r="B5">
-        <v>0.653502209</v>
-      </c>
-      <c r="C5">
-        <v>9.7069930000000006E-3</v>
-      </c>
-      <c r="D5">
-        <v>3911.5133247499998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>1E-4</v>
-      </c>
-      <c r="B6">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="1">
+        <v>1E-4</v>
+      </c>
+      <c r="B33" s="1">
         <v>1.8598445000000002E-2</v>
       </c>
-      <c r="C6">
+      <c r="C33" s="1">
         <v>3.7669257999999997E-2</v>
       </c>
-      <c r="D6">
+      <c r="D33" s="1">
         <v>-132.51586294649999</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>1E-4</v>
-      </c>
-      <c r="B7">
-        <v>1.3826926E-2</v>
-      </c>
-      <c r="C7">
-        <v>3.7099310000000001E-3</v>
-      </c>
-      <c r="D7">
-        <v>813.2296953</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>1E-4</v>
-      </c>
-      <c r="B8">
-        <v>2.0133960000000002E-3</v>
-      </c>
-      <c r="C8">
-        <v>0.58600680999999999</v>
-      </c>
-      <c r="D8">
-        <v>1453.20748725</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>1E-4</v>
-      </c>
-      <c r="B9">
-        <v>0.29416244200000002</v>
-      </c>
-      <c r="C9">
-        <v>3.4769330000000002E-3</v>
-      </c>
-      <c r="D9">
-        <v>2165.29505075</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>1E-4</v>
-      </c>
-      <c r="B10">
-        <v>5.2151409000000003E-2</v>
-      </c>
-      <c r="C10">
-        <v>1.6056401000000001E-2</v>
-      </c>
-      <c r="D10">
-        <v>899.07043136000004</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>1E-4</v>
-      </c>
-      <c r="B11">
-        <v>0.59090410599999998</v>
-      </c>
-      <c r="C11">
-        <v>0.75721505499999997</v>
-      </c>
-      <c r="D11">
-        <v>1912.052664925</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>1E-4</v>
-      </c>
-      <c r="B12">
-        <v>0.23317315399999999</v>
-      </c>
-      <c r="C12">
-        <v>2.0254294999999999E-2</v>
-      </c>
-      <c r="D12">
-        <v>4505.40291875</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>1E-4</v>
-      </c>
-      <c r="B13">
-        <v>1.0292209E-2</v>
-      </c>
-      <c r="C13">
-        <v>8.4481729999999998E-3</v>
-      </c>
-      <c r="D13">
-        <v>2598.3565992499998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>1E-4</v>
-      </c>
-      <c r="B14">
-        <v>2.674114E-3</v>
-      </c>
-      <c r="C14">
-        <v>2.54425E-2</v>
-      </c>
-      <c r="D14">
-        <v>1353.9435281999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>1E-4</v>
-      </c>
-      <c r="B15">
-        <v>1.2057157000000001E-2</v>
-      </c>
-      <c r="C15">
-        <v>0.81009397900000002</v>
-      </c>
-      <c r="D15">
-        <v>2536.8813452499999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>1E-4</v>
-      </c>
-      <c r="B16">
-        <v>8.0714930000000008E-3</v>
-      </c>
-      <c r="C16">
-        <v>0.10003920500000001</v>
-      </c>
-      <c r="D16">
-        <v>3140.092005</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>1E-4</v>
-      </c>
-      <c r="B17">
-        <v>6.4415100000000001E-3</v>
-      </c>
-      <c r="C17">
-        <v>1.2496720000000001E-3</v>
-      </c>
-      <c r="D17">
-        <v>3890.2474617500002</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18">
-        <v>1E-4</v>
-      </c>
-      <c r="B18">
-        <v>1.497338E-3</v>
-      </c>
-      <c r="C18">
-        <v>0.13228768099999999</v>
-      </c>
-      <c r="D18">
-        <v>2434.4130709999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>1E-4</v>
-      </c>
-      <c r="B19">
-        <v>4.9774750000000003E-3</v>
-      </c>
-      <c r="C19">
-        <v>5.4831019000000002E-2</v>
-      </c>
-      <c r="D19">
-        <v>3354.6065990000002</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>1E-4</v>
-      </c>
-      <c r="B20">
-        <v>3.3296083999999997E-2</v>
-      </c>
-      <c r="C20">
-        <v>8.4645748000000007E-2</v>
-      </c>
-      <c r="D20">
-        <v>4475.1998732499997</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21">
-        <v>1E-4</v>
-      </c>
-      <c r="B21">
-        <v>7.7832249000000006E-2</v>
-      </c>
-      <c r="C21">
-        <v>1.0975659999999999E-3</v>
-      </c>
-      <c r="D21">
-        <v>5462.3096447500002</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22">
-        <v>1E-4</v>
-      </c>
-      <c r="B22">
-        <v>0.36215188100000001</v>
-      </c>
-      <c r="C22">
-        <v>0.148571812</v>
-      </c>
-      <c r="D22">
-        <v>4884.9175127500002</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23">
-        <v>1E-4</v>
-      </c>
-      <c r="B23">
-        <v>4.4002681000000002E-2</v>
-      </c>
-      <c r="C23">
-        <v>2.9292954999999999E-2</v>
-      </c>
-      <c r="D23">
-        <v>5065.291878</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24">
-        <v>1E-4</v>
-      </c>
-      <c r="B24">
-        <v>0.13645116500000001</v>
-      </c>
-      <c r="C24">
-        <v>4.0931093000000002E-2</v>
-      </c>
-      <c r="D24">
-        <v>6474.1021575000004</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25">
-        <v>1E-4</v>
-      </c>
-      <c r="B25">
-        <v>2.8054831999999998E-2</v>
-      </c>
-      <c r="C25">
-        <v>2.5393009999999999E-3</v>
-      </c>
-      <c r="D25">
-        <v>7242.645939</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26">
-        <v>1E-4</v>
-      </c>
-      <c r="B26">
-        <v>9.7710587000000002E-2</v>
-      </c>
-      <c r="C26">
-        <v>0.211593646</v>
-      </c>
-      <c r="D26">
-        <v>6402.72208125</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27">
-        <v>1E-4</v>
-      </c>
-      <c r="B27">
-        <v>1.2002880000000001E-3</v>
-      </c>
-      <c r="C27">
-        <v>1.246567E-2</v>
-      </c>
-      <c r="D27">
-        <v>6312.9441622499999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28">
-        <v>1E-4</v>
-      </c>
-      <c r="B28">
-        <v>2.3438180999999999E-2</v>
-      </c>
-      <c r="C28">
-        <v>0.235570958</v>
-      </c>
-      <c r="D28">
-        <v>7167.6237312499998</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29">
-        <v>1E-4</v>
-      </c>
-      <c r="B29">
-        <v>6.3274079999999996E-2</v>
-      </c>
-      <c r="C29">
-        <v>0.51837422200000005</v>
-      </c>
-      <c r="D29">
-        <v>8286.1643399999994</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30">
-        <v>1E-4</v>
-      </c>
-      <c r="B30">
-        <v>3.0869280000000001E-3</v>
-      </c>
-      <c r="C30">
-        <v>5.8427339999999996E-3</v>
-      </c>
-      <c r="D30">
-        <v>7589.2893402500004</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31">
-        <v>1E-4</v>
-      </c>
-      <c r="B31">
-        <v>0.97027319000000001</v>
-      </c>
-      <c r="C31">
-        <v>6.1840059000000003E-2</v>
-      </c>
-      <c r="D31">
-        <v>13870.532992500001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32">
-        <v>1E-4</v>
-      </c>
-      <c r="B32">
-        <v>0.152879814</v>
-      </c>
-      <c r="C32">
-        <v>4.745768E-3</v>
-      </c>
-      <c r="D32">
-        <v>9816.5989852500006</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33">
-        <v>1E-4</v>
-      </c>
-      <c r="B33">
-        <v>0.19203820799999999</v>
-      </c>
-      <c r="C33">
-        <v>0.35750437200000001</v>
-      </c>
-      <c r="D33">
-        <v>10792.6332475</v>
-      </c>
-    </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34">
-        <v>0.01</v>
-      </c>
-      <c r="B34">
-        <v>5.6008911000000002E-2</v>
-      </c>
-      <c r="C34">
-        <v>3.093901E-3</v>
-      </c>
-      <c r="D34">
-        <v>2057.6681471249999</v>
+      <c r="A34" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B34" s="1">
+        <v>0.92946733800000003</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1.6635283000000001E-2</v>
+      </c>
+      <c r="D34" s="1">
+        <v>65054.2068525</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35">
-        <v>0.01</v>
-      </c>
-      <c r="B35">
-        <v>0.15182020099999999</v>
-      </c>
-      <c r="C35">
-        <v>0.43453321</v>
-      </c>
-      <c r="D35">
-        <v>1568.4676393499999</v>
+      <c r="A35" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B35" s="1">
+        <v>0.73689710399999997</v>
+      </c>
+      <c r="C35" s="1">
+        <v>0.18438611099999999</v>
+      </c>
+      <c r="D35" s="1">
+        <v>43097.630080000003</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36">
-        <v>0.01</v>
-      </c>
-      <c r="B36">
-        <v>1.0093803E-2</v>
-      </c>
-      <c r="C36">
-        <v>0.88486579200000004</v>
-      </c>
-      <c r="D36">
-        <v>-361.96700507499997</v>
+      <c r="A36" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B36" s="1">
+        <v>0.22605519900000001</v>
+      </c>
+      <c r="C36" s="1">
+        <v>4.0735200999999999E-2</v>
+      </c>
+      <c r="D36" s="1">
+        <v>25527.414339999999</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37">
-        <v>0.01</v>
-      </c>
-      <c r="B37">
+      <c r="A37" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B37" s="1">
+        <v>0.28719808600000002</v>
+      </c>
+      <c r="C37" s="1">
+        <v>8.9638210999999995E-2</v>
+      </c>
+      <c r="D37" s="1">
+        <v>25192.398477499999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B38" s="1">
+        <v>0.60371082499999995</v>
+      </c>
+      <c r="C38" s="1">
+        <v>6.6112819999999996E-3</v>
+      </c>
+      <c r="D38" s="1">
+        <v>16839.68591475</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B39" s="1">
+        <v>0.108762808</v>
+      </c>
+      <c r="C39" s="1">
+        <v>0.14347787000000001</v>
+      </c>
+      <c r="D39" s="1">
+        <v>10562.2493655</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B40" s="1">
+        <v>2.6315785000000001E-2</v>
+      </c>
+      <c r="C40" s="1">
+        <v>9.8714389999999992E-3</v>
+      </c>
+      <c r="D40" s="1">
+        <v>9656.7956845000008</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B41" s="1">
         <v>0.11844879699999999</v>
       </c>
-      <c r="C37">
+      <c r="C41" s="1">
         <v>1.1756654E-2</v>
       </c>
-      <c r="D37">
+      <c r="D41" s="1">
         <v>8593.1757610000004</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38">
-        <v>0.01</v>
-      </c>
-      <c r="B38">
-        <v>1.6712766E-2</v>
-      </c>
-      <c r="C38">
-        <v>1.2253699999999999E-3</v>
-      </c>
-      <c r="D38">
-        <v>-242.73159896499999</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39">
-        <v>0.01</v>
-      </c>
-      <c r="B39">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B42" s="1">
+        <v>8.6698849999999994E-2</v>
+      </c>
+      <c r="C42" s="1">
+        <v>4.825195E-3</v>
+      </c>
+      <c r="D42" s="1">
+        <v>8441.34834925</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B43" s="1">
+        <v>6.2587501000000004E-2</v>
+      </c>
+      <c r="C43" s="1">
+        <v>5.3059803000000003E-2</v>
+      </c>
+      <c r="D43" s="1">
+        <v>7864.6573605000003</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B44" s="1">
+        <v>2.4344750000000002E-3</v>
+      </c>
+      <c r="C44" s="1">
+        <v>1.5769219999999999E-3</v>
+      </c>
+      <c r="D44" s="1">
+        <v>7724.8223349999998</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B45" s="1">
+        <v>4.4871609999999999E-3</v>
+      </c>
+      <c r="C45" s="1">
+        <v>7.27313E-3</v>
+      </c>
+      <c r="D45" s="1">
+        <v>7503.5596447500002</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B46" s="1">
+        <v>1.868106E-3</v>
+      </c>
+      <c r="C46" s="1">
+        <v>7.2655726000000004E-2</v>
+      </c>
+      <c r="D46" s="1">
+        <v>7261.0691624999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B47" s="1">
+        <v>0.19760839199999999</v>
+      </c>
+      <c r="C47" s="1">
+        <v>1.4283550000000001E-3</v>
+      </c>
+      <c r="D47" s="1">
+        <v>6269.4733502500003</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B48" s="1">
+        <v>0.43566181199999998</v>
+      </c>
+      <c r="C48" s="1">
+        <v>2.0735079999999999E-3</v>
+      </c>
+      <c r="D48" s="1">
+        <v>6220.9263959999998</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B49" s="1">
         <v>0.410383832</v>
       </c>
-      <c r="C39">
+      <c r="C49" s="1">
         <v>0.75171392599999998</v>
       </c>
-      <c r="D39">
+      <c r="D49" s="1">
         <v>5986.0025382499998</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40">
-        <v>0.01</v>
-      </c>
-      <c r="B40">
-        <v>4.6038720000000002E-3</v>
-      </c>
-      <c r="C40">
-        <v>3.3574522000000002E-2</v>
-      </c>
-      <c r="D40">
-        <v>-721.80837562500005</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41">
-        <v>0.01</v>
-      </c>
-      <c r="B41">
-        <v>7.617202E-3</v>
-      </c>
-      <c r="C41">
-        <v>2.7287129999999998E-3</v>
-      </c>
-      <c r="D41">
-        <v>-101.86865482499999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42">
-        <v>0.01</v>
-      </c>
-      <c r="B42">
-        <v>1.0914712E-2</v>
-      </c>
-      <c r="C42">
-        <v>1.6090496999999999E-2</v>
-      </c>
-      <c r="D42">
-        <v>385.72335022499999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43">
-        <v>0.01</v>
-      </c>
-      <c r="B43">
-        <v>1.305507E-3</v>
-      </c>
-      <c r="C43">
-        <v>0.27848552999999998</v>
-      </c>
-      <c r="D43">
-        <v>-192.734771575</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44">
-        <v>0.01</v>
-      </c>
-      <c r="B44">
-        <v>0.60371082499999995</v>
-      </c>
-      <c r="C44">
-        <v>6.6112819999999996E-3</v>
-      </c>
-      <c r="D44">
-        <v>16839.68591475</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45">
-        <v>0.01</v>
-      </c>
-      <c r="B45">
-        <v>0.28719808600000002</v>
-      </c>
-      <c r="C45">
-        <v>8.9638210999999995E-2</v>
-      </c>
-      <c r="D45">
-        <v>25192.398477499999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46">
-        <v>0.01</v>
-      </c>
-      <c r="B46">
-        <v>0.22605519900000001</v>
-      </c>
-      <c r="C46">
-        <v>4.0735200999999999E-2</v>
-      </c>
-      <c r="D46">
-        <v>25527.414339999999</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47">
-        <v>0.01</v>
-      </c>
-      <c r="B47">
-        <v>3.8557267999999999E-2</v>
-      </c>
-      <c r="C47">
-        <v>3.0525004000000001E-2</v>
-      </c>
-      <c r="D47">
-        <v>3763.10913725</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48">
-        <v>0.01</v>
-      </c>
-      <c r="B48">
-        <v>4.6358941000000001E-2</v>
-      </c>
-      <c r="C48">
-        <v>0.34746024399999997</v>
-      </c>
-      <c r="D48">
-        <v>1183.39149735</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49">
-        <v>0.01</v>
-      </c>
-      <c r="B49">
-        <v>1.9688739999999998E-3</v>
-      </c>
-      <c r="C49">
-        <v>2.3227589E-2</v>
-      </c>
-      <c r="D49">
-        <v>1431.0152282500001</v>
-      </c>
-    </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50">
-        <v>0.01</v>
-      </c>
-      <c r="B50">
-        <v>5.8847179999999997E-3</v>
-      </c>
-      <c r="C50">
-        <v>0.106593115</v>
-      </c>
-      <c r="D50">
-        <v>2190.0951777499999</v>
+      <c r="A50" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B50" s="1">
+        <v>1.0606560000000001E-3</v>
+      </c>
+      <c r="C50" s="1">
+        <v>4.3800610000000002E-3</v>
+      </c>
+      <c r="D50" s="1">
+        <v>5347.0399747499996</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51">
-        <v>0.01</v>
-      </c>
-      <c r="B51">
-        <v>0.43566181199999998</v>
-      </c>
-      <c r="C51">
-        <v>2.0735079999999999E-3</v>
-      </c>
-      <c r="D51">
-        <v>6220.9263959999998</v>
+      <c r="A51" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B51" s="1">
+        <v>3.4578590000000002E-3</v>
+      </c>
+      <c r="C51" s="1">
+        <v>0.64203762099999995</v>
+      </c>
+      <c r="D51" s="1">
+        <v>5269.6224620000003</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
@@ -1086,615 +1088,615 @@
         <v>0.01</v>
       </c>
       <c r="B52" s="1">
-        <v>0.92946733800000003</v>
+        <v>1.3827492E-2</v>
       </c>
       <c r="C52" s="1">
-        <v>1.6635283000000001E-2</v>
+        <v>0.12706197599999999</v>
       </c>
       <c r="D52" s="1">
-        <v>65054.2068525</v>
+        <v>4301.3832487500003</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53">
-        <v>0.01</v>
-      </c>
-      <c r="B53">
-        <v>0.19760839199999999</v>
-      </c>
-      <c r="C53">
-        <v>1.4283550000000001E-3</v>
-      </c>
-      <c r="D53">
-        <v>6269.4733502500003</v>
+      <c r="A53" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B53" s="1">
+        <v>2.1074565999999999E-2</v>
+      </c>
+      <c r="C53" s="1">
+        <v>0.23216314599999999</v>
+      </c>
+      <c r="D53" s="1">
+        <v>3843.0964469999999</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54">
-        <v>0.01</v>
-      </c>
-      <c r="B54">
-        <v>8.6698849999999994E-2</v>
-      </c>
-      <c r="C54">
-        <v>4.825195E-3</v>
-      </c>
-      <c r="D54">
-        <v>8441.34834925</v>
+      <c r="A54" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B54" s="1">
+        <v>3.8557267999999999E-2</v>
+      </c>
+      <c r="C54" s="1">
+        <v>3.0525004000000001E-2</v>
+      </c>
+      <c r="D54" s="1">
+        <v>3763.10913725</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55">
-        <v>0.01</v>
-      </c>
-      <c r="B55">
-        <v>2.1074565999999999E-2</v>
-      </c>
-      <c r="C55">
-        <v>0.23216314599999999</v>
-      </c>
-      <c r="D55">
-        <v>3843.0964469999999</v>
+      <c r="A55" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B55" s="1">
+        <v>5.8847179999999997E-3</v>
+      </c>
+      <c r="C55" s="1">
+        <v>0.106593115</v>
+      </c>
+      <c r="D55" s="1">
+        <v>2190.0951777499999</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56">
-        <v>0.01</v>
-      </c>
-      <c r="B56">
-        <v>1.3827492E-2</v>
-      </c>
-      <c r="C56">
-        <v>0.12706197599999999</v>
-      </c>
-      <c r="D56">
-        <v>4301.3832487500003</v>
+      <c r="A56" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B56" s="1">
+        <v>5.6008911000000002E-2</v>
+      </c>
+      <c r="C56" s="1">
+        <v>3.093901E-3</v>
+      </c>
+      <c r="D56" s="1">
+        <v>2057.6681471249999</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57">
-        <v>0.01</v>
-      </c>
-      <c r="B57">
-        <v>6.2587501000000004E-2</v>
-      </c>
-      <c r="C57">
-        <v>5.3059803000000003E-2</v>
-      </c>
-      <c r="D57">
-        <v>7864.6573605000003</v>
+      <c r="A57" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B57" s="1">
+        <v>0.15182020099999999</v>
+      </c>
+      <c r="C57" s="1">
+        <v>0.43453321</v>
+      </c>
+      <c r="D57" s="1">
+        <v>1568.4676393499999</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58">
-        <v>0.01</v>
-      </c>
-      <c r="B58">
-        <v>0.108762808</v>
-      </c>
-      <c r="C58">
-        <v>0.14347787000000001</v>
-      </c>
-      <c r="D58">
-        <v>10562.2493655</v>
+      <c r="A58" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B58" s="1">
+        <v>1.9688739999999998E-3</v>
+      </c>
+      <c r="C58" s="1">
+        <v>2.3227589E-2</v>
+      </c>
+      <c r="D58" s="1">
+        <v>1431.0152282500001</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59">
-        <v>0.01</v>
-      </c>
-      <c r="B59">
-        <v>0.73689710399999997</v>
-      </c>
-      <c r="C59">
-        <v>0.18438611099999999</v>
-      </c>
-      <c r="D59">
-        <v>43097.630080000003</v>
+      <c r="A59" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B59" s="1">
+        <v>4.6358941000000001E-2</v>
+      </c>
+      <c r="C59" s="1">
+        <v>0.34746024399999997</v>
+      </c>
+      <c r="D59" s="1">
+        <v>1183.39149735</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60">
-        <v>0.01</v>
-      </c>
-      <c r="B60">
-        <v>3.4578590000000002E-3</v>
-      </c>
-      <c r="C60">
-        <v>0.64203762099999995</v>
-      </c>
-      <c r="D60">
-        <v>5269.6224620000003</v>
+      <c r="A60" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B60" s="1">
+        <v>1.0914712E-2</v>
+      </c>
+      <c r="C60" s="1">
+        <v>1.6090496999999999E-2</v>
+      </c>
+      <c r="D60" s="1">
+        <v>385.72335022499999</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61">
-        <v>0.01</v>
-      </c>
-      <c r="B61">
-        <v>1.0606560000000001E-3</v>
-      </c>
-      <c r="C61">
-        <v>4.3800610000000002E-3</v>
-      </c>
-      <c r="D61">
-        <v>5347.0399747499996</v>
+      <c r="A61" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B61" s="1">
+        <v>7.617202E-3</v>
+      </c>
+      <c r="C61" s="1">
+        <v>2.7287129999999998E-3</v>
+      </c>
+      <c r="D61" s="1">
+        <v>-101.86865482499999</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62">
-        <v>0.01</v>
-      </c>
-      <c r="B62">
-        <v>1.868106E-3</v>
-      </c>
-      <c r="C62">
-        <v>7.2655726000000004E-2</v>
-      </c>
-      <c r="D62">
-        <v>7261.0691624999999</v>
+      <c r="A62" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B62" s="1">
+        <v>1.305507E-3</v>
+      </c>
+      <c r="C62" s="1">
+        <v>0.27848552999999998</v>
+      </c>
+      <c r="D62" s="1">
+        <v>-192.734771575</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63">
-        <v>0.01</v>
-      </c>
-      <c r="B63">
-        <v>2.6315785000000001E-2</v>
-      </c>
-      <c r="C63">
-        <v>9.8714389999999992E-3</v>
-      </c>
-      <c r="D63">
-        <v>9656.7956845000008</v>
+      <c r="A63" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B63" s="1">
+        <v>1.6712766E-2</v>
+      </c>
+      <c r="C63" s="1">
+        <v>1.2253699999999999E-3</v>
+      </c>
+      <c r="D63" s="1">
+        <v>-242.73159896499999</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64">
-        <v>0.01</v>
-      </c>
-      <c r="B64">
-        <v>2.4344750000000002E-3</v>
-      </c>
-      <c r="C64">
-        <v>1.5769219999999999E-3</v>
-      </c>
-      <c r="D64">
-        <v>7724.8223349999998</v>
+      <c r="A64" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B64" s="1">
+        <v>1.0093803E-2</v>
+      </c>
+      <c r="C64" s="1">
+        <v>0.88486579200000004</v>
+      </c>
+      <c r="D64" s="1">
+        <v>-361.96700507499997</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65">
-        <v>0.01</v>
-      </c>
-      <c r="B65">
-        <v>4.4871609999999999E-3</v>
-      </c>
-      <c r="C65">
-        <v>7.27313E-3</v>
-      </c>
-      <c r="D65">
-        <v>7503.5596447500002</v>
+      <c r="A65" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="B65" s="1">
+        <v>4.6038720000000002E-3</v>
+      </c>
+      <c r="C65" s="1">
+        <v>3.3574522000000002E-2</v>
+      </c>
+      <c r="D65" s="1">
+        <v>-721.80837562500005</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66">
-        <v>1</v>
-      </c>
-      <c r="B66">
+      <c r="A66" s="1">
+        <v>1</v>
+      </c>
+      <c r="B66" s="1">
+        <v>0.87460116300000001</v>
+      </c>
+      <c r="C66" s="1">
+        <v>0.50829114799999997</v>
+      </c>
+      <c r="D66" s="1">
+        <v>60215.111040000003</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" s="1">
+        <v>1</v>
+      </c>
+      <c r="B67" s="1">
+        <v>0.265689966</v>
+      </c>
+      <c r="C67" s="1">
+        <v>3.6664359999999999E-3</v>
+      </c>
+      <c r="D67" s="1">
+        <v>40327.262054999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" s="1">
+        <v>1</v>
+      </c>
+      <c r="B68" s="1">
+        <v>0.456044008</v>
+      </c>
+      <c r="C68" s="1">
+        <v>7.0786249999999998E-3</v>
+      </c>
+      <c r="D68" s="1">
+        <v>30486.123094999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" s="1">
+        <v>1</v>
+      </c>
+      <c r="B69" s="1">
+        <v>0.69212307699999998</v>
+      </c>
+      <c r="C69" s="1">
+        <v>1.7836849999999999E-3</v>
+      </c>
+      <c r="D69" s="1">
+        <v>25546.824237500001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" s="1">
+        <v>1</v>
+      </c>
+      <c r="B70" s="1">
+        <v>0.11033149</v>
+      </c>
+      <c r="C70" s="1">
+        <v>1.0873090000000001E-3</v>
+      </c>
+      <c r="D70" s="1">
+        <v>17108.629440000001</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" s="1">
+        <v>1</v>
+      </c>
+      <c r="B71" s="1">
+        <v>0.29276129499999998</v>
+      </c>
+      <c r="C71" s="1">
+        <v>0.21389501499999999</v>
+      </c>
+      <c r="D71" s="1">
+        <v>10532.81408475</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" s="1">
+        <v>1</v>
+      </c>
+      <c r="B72" s="1">
+        <v>6.3086988999999996E-2</v>
+      </c>
+      <c r="C72" s="1">
+        <v>0.141467806</v>
+      </c>
+      <c r="D72" s="1">
+        <v>8963.6611675000004</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" s="1">
+        <v>1</v>
+      </c>
+      <c r="B73" s="1">
+        <v>0.13598734400000001</v>
+      </c>
+      <c r="C73" s="1">
+        <v>0.76118231999999997</v>
+      </c>
+      <c r="D73" s="1">
+        <v>7761.8623097500003</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" s="1">
+        <v>1</v>
+      </c>
+      <c r="B74" s="1">
+        <v>5.2952310000000002E-2</v>
+      </c>
+      <c r="C74" s="1">
+        <v>3.4455050000000002E-3</v>
+      </c>
+      <c r="D74" s="1">
+        <v>6848.8578680000001</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" s="1">
+        <v>1</v>
+      </c>
+      <c r="B75" s="1">
+        <v>1.6188659000000001E-2</v>
+      </c>
+      <c r="C75" s="1">
+        <v>2.9689E-2</v>
+      </c>
+      <c r="D75" s="1">
+        <v>6581.3071065000004</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" s="1">
+        <v>1</v>
+      </c>
+      <c r="B76" s="1">
+        <v>2.18046E-3</v>
+      </c>
+      <c r="C76" s="1">
+        <v>0.57079832399999997</v>
+      </c>
+      <c r="D76" s="1">
+        <v>6560.9835025000002</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" s="1">
+        <v>1</v>
+      </c>
+      <c r="B77" s="1">
+        <v>0.17578461500000001</v>
+      </c>
+      <c r="C77" s="1">
+        <v>5.6172774000000002E-2</v>
+      </c>
+      <c r="D77" s="1">
+        <v>6349.6478427499997</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" s="1">
+        <v>1</v>
+      </c>
+      <c r="B78" s="1">
+        <v>0.41161421599999998</v>
+      </c>
+      <c r="C78" s="1">
+        <v>0.11442783500000001</v>
+      </c>
+      <c r="D78" s="1">
+        <v>5983.895939</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" s="1">
+        <v>1</v>
+      </c>
+      <c r="B79" s="1">
+        <v>5.2354139999999999E-3</v>
+      </c>
+      <c r="C79" s="1">
+        <v>0.25281826899999998</v>
+      </c>
+      <c r="D79" s="1">
+        <v>5455.6630709999999</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" s="1">
+        <v>1</v>
+      </c>
+      <c r="B80" s="1">
+        <v>2.3245913E-2</v>
+      </c>
+      <c r="C80" s="1">
+        <v>2.8355989999999998E-3</v>
+      </c>
+      <c r="D80" s="1">
+        <v>4816.5862942499998</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" s="1">
+        <v>1</v>
+      </c>
+      <c r="B81" s="1">
+        <v>2.7012950000000001E-2</v>
+      </c>
+      <c r="C81" s="1">
+        <v>6.7603828000000005E-2</v>
+      </c>
+      <c r="D81" s="1">
+        <v>4764.6541877500003</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" s="1">
+        <v>1</v>
+      </c>
+      <c r="B82" s="1">
         <v>4.2605628999999999E-2</v>
       </c>
-      <c r="C66">
+      <c r="C82" s="1">
         <v>0.31662526800000002</v>
       </c>
-      <c r="D66">
+      <c r="D82" s="1">
         <v>4165.7614215000003</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67">
-        <v>1</v>
-      </c>
-      <c r="B67">
-        <v>0.456044008</v>
-      </c>
-      <c r="C67">
-        <v>7.0786249999999998E-3</v>
-      </c>
-      <c r="D67">
-        <v>30486.123094999999</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68">
-        <v>1</v>
-      </c>
-      <c r="B68">
-        <v>0.69212307699999998</v>
-      </c>
-      <c r="C68">
-        <v>1.7836849999999999E-3</v>
-      </c>
-      <c r="D68">
-        <v>25546.824237500001</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69">
-        <v>1</v>
-      </c>
-      <c r="B69">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" s="1">
+        <v>1</v>
+      </c>
+      <c r="B83" s="1">
+        <v>1.1894497E-2</v>
+      </c>
+      <c r="C83" s="1">
+        <v>5.9016980000000004E-3</v>
+      </c>
+      <c r="D83" s="1">
+        <v>3599.428934</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" s="1">
+        <v>1</v>
+      </c>
+      <c r="B84" s="1">
+        <v>2.0324828E-2</v>
+      </c>
+      <c r="C84" s="1">
+        <v>0.94246236500000002</v>
+      </c>
+      <c r="D84" s="1">
+        <v>3556.157995</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" s="1">
+        <v>1</v>
+      </c>
+      <c r="B85" s="1">
+        <v>2.7729320000000001E-3</v>
+      </c>
+      <c r="C85" s="1">
+        <v>5.0343530000000001E-3</v>
+      </c>
+      <c r="D85" s="1">
+        <v>2897.3857867500001</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" s="1">
+        <v>1</v>
+      </c>
+      <c r="B86" s="1">
+        <v>4.3494049999999998E-3</v>
+      </c>
+      <c r="C86" s="1">
+        <v>1.1481333999999999E-2</v>
+      </c>
+      <c r="D86" s="1">
+        <v>2712.3857870000002</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87" s="1">
+        <v>1</v>
+      </c>
+      <c r="B87" s="1">
+        <v>3.6150422000000001E-2</v>
+      </c>
+      <c r="C87" s="1">
+        <v>9.5587980000000003E-3</v>
+      </c>
+      <c r="D87" s="1">
+        <v>2023.217005</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88" s="1">
+        <v>1</v>
+      </c>
+      <c r="B88" s="1">
+        <v>1.0447410000000001E-3</v>
+      </c>
+      <c r="C88" s="1">
+        <v>0.159683723</v>
+      </c>
+      <c r="D88" s="1">
+        <v>1968.3597715000001</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89" s="1">
+        <v>1</v>
+      </c>
+      <c r="B89" s="1">
+        <v>1.5030569999999999E-3</v>
+      </c>
+      <c r="C89" s="1">
+        <v>2.2894349999999998E-3</v>
+      </c>
+      <c r="D89" s="1">
+        <v>1885.523477</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90" s="1">
+        <v>1</v>
+      </c>
+      <c r="B90" s="1">
+        <v>6.4556199999999996E-3</v>
+      </c>
+      <c r="C90" s="1">
+        <v>1.5042359999999999E-3</v>
+      </c>
+      <c r="D90" s="1">
+        <v>1683.1503807500001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91" s="1">
+        <v>1</v>
+      </c>
+      <c r="B91" s="1">
+        <v>9.6973860000000005E-3</v>
+      </c>
+      <c r="C91" s="1">
+        <v>7.6256213000000003E-2</v>
+      </c>
+      <c r="D91" s="1">
+        <v>599.27030454500004</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92" s="1">
+        <v>1</v>
+      </c>
+      <c r="B92" s="1">
         <v>3.4769050000000002E-3</v>
       </c>
-      <c r="C69">
+      <c r="C92" s="1">
         <v>4.5569369999999998E-2</v>
       </c>
-      <c r="D69">
+      <c r="D92" s="1">
         <v>512.22398477249999</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70">
-        <v>1</v>
-      </c>
-      <c r="B70">
-        <v>4.3494049999999998E-3</v>
-      </c>
-      <c r="C70">
-        <v>1.1481333999999999E-2</v>
-      </c>
-      <c r="D70">
-        <v>2712.3857870000002</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71">
-        <v>1</v>
-      </c>
-      <c r="B71">
-        <v>6.4556199999999996E-3</v>
-      </c>
-      <c r="C71">
-        <v>1.5042359999999999E-3</v>
-      </c>
-      <c r="D71">
-        <v>1683.1503807500001</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72">
-        <v>1</v>
-      </c>
-      <c r="B72">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93" s="1">
+        <v>1</v>
+      </c>
+      <c r="B93" s="1">
+        <v>7.6548379999999997E-3</v>
+      </c>
+      <c r="C93" s="1">
+        <v>0.38417770800000001</v>
+      </c>
+      <c r="D93" s="1">
+        <v>192.4968274</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94" s="1">
+        <v>1</v>
+      </c>
+      <c r="B94" s="1">
+        <v>1.789601E-3</v>
+      </c>
+      <c r="C94" s="1">
+        <v>2.1764748E-2</v>
+      </c>
+      <c r="D94" s="1">
+        <v>122.17005076</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" s="1">
+        <v>1</v>
+      </c>
+      <c r="B95" s="1">
         <v>0.52990120200000002</v>
       </c>
-      <c r="C72">
+      <c r="C95" s="1">
         <v>3.6510218999999997E-2</v>
       </c>
-      <c r="D72">
+      <c r="D95" s="1">
         <v>-420.79631982500001</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73">
-        <v>1</v>
-      </c>
-      <c r="B73">
-        <v>7.6548379999999997E-3</v>
-      </c>
-      <c r="C73">
-        <v>0.38417770800000001</v>
-      </c>
-      <c r="D73">
-        <v>192.4968274</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74">
-        <v>1</v>
-      </c>
-      <c r="B74">
-        <v>2.7729320000000001E-3</v>
-      </c>
-      <c r="C74">
-        <v>5.0343530000000001E-3</v>
-      </c>
-      <c r="D74">
-        <v>2897.3857867500001</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75">
-        <v>1</v>
-      </c>
-      <c r="B75">
-        <v>1.0447410000000001E-3</v>
-      </c>
-      <c r="C75">
-        <v>0.159683723</v>
-      </c>
-      <c r="D75">
-        <v>1968.3597715000001</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76">
-        <v>1</v>
-      </c>
-      <c r="B76">
-        <v>9.6973860000000005E-3</v>
-      </c>
-      <c r="C76">
-        <v>7.6256213000000003E-2</v>
-      </c>
-      <c r="D76">
-        <v>599.27030454500004</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77">
-        <v>1</v>
-      </c>
-      <c r="B77">
-        <v>1.789601E-3</v>
-      </c>
-      <c r="C77">
-        <v>2.1764748E-2</v>
-      </c>
-      <c r="D77">
-        <v>122.17005076</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78">
-        <v>1</v>
-      </c>
-      <c r="B78">
-        <v>3.6150422000000001E-2</v>
-      </c>
-      <c r="C78">
-        <v>9.5587980000000003E-3</v>
-      </c>
-      <c r="D78">
-        <v>2023.217005</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79">
-        <v>1</v>
-      </c>
-      <c r="B79">
-        <v>2.0324828E-2</v>
-      </c>
-      <c r="C79">
-        <v>0.94246236500000002</v>
-      </c>
-      <c r="D79">
-        <v>3556.157995</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80">
-        <v>1</v>
-      </c>
-      <c r="B80">
-        <v>1.5030569999999999E-3</v>
-      </c>
-      <c r="C80">
-        <v>2.2894349999999998E-3</v>
-      </c>
-      <c r="D80">
-        <v>1885.523477</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81">
-        <v>1</v>
-      </c>
-      <c r="B81">
-        <v>8.1719082999999998E-2</v>
-      </c>
-      <c r="C81">
-        <v>1.8188362E-2</v>
-      </c>
-      <c r="D81">
-        <v>-1049.6288070999999</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82">
-        <v>1</v>
-      </c>
-      <c r="B82">
-        <v>0.265689966</v>
-      </c>
-      <c r="C82">
-        <v>3.6664359999999999E-3</v>
-      </c>
-      <c r="D82">
-        <v>40327.262054999999</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83">
-        <v>1</v>
-      </c>
-      <c r="B83">
-        <v>0.13598734400000001</v>
-      </c>
-      <c r="C83">
-        <v>0.76118231999999997</v>
-      </c>
-      <c r="D83">
-        <v>7761.8623097500003</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84">
-        <v>1</v>
-      </c>
-      <c r="B84">
-        <v>0.20160655599999999</v>
-      </c>
-      <c r="C84">
-        <v>1.4644999000000001E-2</v>
-      </c>
-      <c r="D84">
-        <v>-954.95875642500005</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85">
-        <v>1</v>
-      </c>
-      <c r="B85">
-        <v>0.29276129499999998</v>
-      </c>
-      <c r="C85">
-        <v>0.21389501499999999</v>
-      </c>
-      <c r="D85">
-        <v>10532.81408475</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86">
-        <v>1</v>
-      </c>
-      <c r="B86">
-        <v>1.6188659000000001E-2</v>
-      </c>
-      <c r="C86">
-        <v>2.9689E-2</v>
-      </c>
-      <c r="D86">
-        <v>6581.3071065000004</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A87">
-        <v>1</v>
-      </c>
-      <c r="B87">
-        <v>5.2354139999999999E-3</v>
-      </c>
-      <c r="C87">
-        <v>0.25281826899999998</v>
-      </c>
-      <c r="D87">
-        <v>5455.6630709999999</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88">
-        <v>1</v>
-      </c>
-      <c r="B88">
-        <v>1.1894497E-2</v>
-      </c>
-      <c r="C88">
-        <v>5.9016980000000004E-3</v>
-      </c>
-      <c r="D88">
-        <v>3599.428934</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89">
-        <v>1</v>
-      </c>
-      <c r="B89">
-        <v>0.41161421599999998</v>
-      </c>
-      <c r="C89">
-        <v>0.11442783500000001</v>
-      </c>
-      <c r="D89">
-        <v>5983.895939</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90">
-        <v>1</v>
-      </c>
-      <c r="B90">
-        <v>5.2952310000000002E-2</v>
-      </c>
-      <c r="C90">
-        <v>3.4455050000000002E-3</v>
-      </c>
-      <c r="D90">
-        <v>6848.8578680000001</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91">
-        <v>1</v>
-      </c>
-      <c r="B91">
-        <v>0.17578461500000001</v>
-      </c>
-      <c r="C91">
-        <v>5.6172774000000002E-2</v>
-      </c>
-      <c r="D91">
-        <v>6349.6478427499997</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92">
-        <v>1</v>
-      </c>
-      <c r="B92">
-        <v>2.18046E-3</v>
-      </c>
-      <c r="C92">
-        <v>0.57079832399999997</v>
-      </c>
-      <c r="D92">
-        <v>6560.9835025000002</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93">
-        <v>1</v>
-      </c>
-      <c r="B93">
-        <v>2.7012950000000001E-2</v>
-      </c>
-      <c r="C93">
-        <v>6.7603828000000005E-2</v>
-      </c>
-      <c r="D93">
-        <v>4764.6541877500003</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A94">
-        <v>1</v>
-      </c>
-      <c r="B94">
-        <v>0.11033149</v>
-      </c>
-      <c r="C94">
-        <v>1.0873090000000001E-3</v>
-      </c>
-      <c r="D94">
-        <v>17108.629440000001</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95">
-        <v>1</v>
-      </c>
-      <c r="B95">
-        <v>6.3086988999999996E-2</v>
-      </c>
-      <c r="C95">
-        <v>0.141467806</v>
-      </c>
-      <c r="D95">
-        <v>8963.6611675000004</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
@@ -1702,32 +1704,33 @@
         <v>1</v>
       </c>
       <c r="B96" s="1">
-        <v>0.87460116300000001</v>
+        <v>0.20160655599999999</v>
       </c>
       <c r="C96" s="1">
-        <v>0.50829114799999997</v>
+        <v>1.4644999000000001E-2</v>
       </c>
       <c r="D96" s="1">
-        <v>60215.111040000003</v>
+        <v>-954.95875642500005</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97">
-        <v>1</v>
-      </c>
-      <c r="B97">
-        <v>2.3245913E-2</v>
-      </c>
-      <c r="C97">
-        <v>2.8355989999999998E-3</v>
-      </c>
-      <c r="D97">
-        <v>4816.5862942499998</v>
+      <c r="A97" s="1">
+        <v>1</v>
+      </c>
+      <c r="B97" s="1">
+        <v>8.1719082999999998E-2</v>
+      </c>
+      <c r="C97" s="1">
+        <v>1.8188362E-2</v>
+      </c>
+      <c r="D97" s="1">
+        <v>-1049.6288070999999</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D97">
     <sortCondition ref="A2:A97"/>
+    <sortCondition descending="1" ref="D2:D97"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
